--- a/claude/data/한양이엔지_데이터북_2026-10-22.xlsx
+++ b/claude/data/한양이엔지_데이터북_2026-10-22.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_CCSS경쟁" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_밸류에이션" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_출처" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_현장일정표_정리" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -83,6 +84,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,7 +464,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -624,7 +625,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -825,6 +825,1145 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>연결-별도 차이는 내부거래 제거 포함 근사. 2016~2018 현장 금액은 구 공시 방식</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>현장 일정표(정리본). 출처: 정기보고서 진행률적용 수주상황(2016~18), 연결 건설계약 주석(2020~2026). 금액은 공시된 것만. 예상 행은 추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>고객·팹</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>공사</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>시작</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>종료(최신 완성기한)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>삼성 평택 P1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CCSS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2016.06</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2017.10</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CCSS·장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성 평택 P1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hook-up</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2017.04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2018.02</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성 평택 P1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hook-up Ph3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2017.09</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2018.12</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>삼성 평택 P2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Module(1차)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2018.08</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2021.12</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>삼성 평택 P2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ph1 Hook-up</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2019.12</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2021.11</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성 평택 P2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ph2 Module</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2020.03</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2022.03</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>삼성 평택 P2</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>EUV 하부층 Module</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2021.04</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2022.05</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>삼성 평택 P3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ph1 Module</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2021.06</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2024.02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>삼성 평택 P3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ph1 Hook-up</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2022.03</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2023.12</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성 평택 P3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ph3 Module</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2022.06</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2023.12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>삼성 평택 P3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ph2 Hook-up</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2022.09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2023.12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>삼성 평택 P3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ph3 Hook-up</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2022.12</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2023.12</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>삼성 평택 P4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ph1 Module</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2023.04</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025.02</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>삼성 평택 P4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ph1 BEOL/DRAM</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2023.10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026.07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>삼성 평택 P4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ph1 Hook-up</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2024.05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>삼성 평택 P4</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ph3 CCSS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2024.10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025.12</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CCSS·장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>삼성 평택 P4</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ph3 Hook-up</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025.05</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>삼성 평택 P4</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ph4 Module</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025.09</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026.11</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>삼성 평택 P5</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ph1 일반배관 1공구(1,481억)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026.09</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2027.09</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>삼성 평택 P5</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hook-up(예상)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2027.06</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2029.06</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>예상</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>M16 Ph2 CCSS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2021.08</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2022.10</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>CCSS·장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M16 Ph2 UT배관</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2021.12</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2023.01</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>M15 Ph2A UT배관</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2022.01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2024.07</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M15 Ph2B 폐수처리</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2022.11</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025.06</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>M15X Ph3 UT배관</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2024.11</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026.10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>용인 Y1 Hook-up(예상)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2027.01</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2028.12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>예상</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>삼성 테일러(미국)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CCSS 제작·설치</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2022.12</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CCSS·장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>삼성 테일러(미국)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GCS Hook-up</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2023.11</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026.10</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>삼성 테일러(미국)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Retrofit 케미칼 배관(694억)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025.10</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026.08</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>삼성 테일러(미국)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tool Hook-up</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025.11</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026.12</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>삼성 테일러(미국)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2공장(착공 검토, 예상)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2027.06</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2029.12</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>예상</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>유지보수·기타</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>화성 H/U 유지보수</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2018.11</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2021.12</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>유지보수·기타</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>화성 H2 Hook-up</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2022.07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025.12</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>유지보수·기타</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>화성 15L/16L Hook-up</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2025.01</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025.12</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>유지보수·기타</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>천안·온양 TSP/C2~C4</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2022.07</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1차 배관·모듈</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>유지보수·기타</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>중국 시안 X2 Ph2 Hook-up</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2020.12</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2022.12</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2차 Hook-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>유지보수·기타</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>해외 CDS 패키지(8,073만$)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026.06</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2028.06</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>CCSS·장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P1 양산</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2017.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P2 양산</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2020.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P3 가동</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2022.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Y1 클린룸</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2027.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>P5 가동</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2027.12</t>
         </is>
       </c>
     </row>
@@ -860,7 +1999,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -1310,7 +2448,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2429,7 +3566,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2726,7 +3862,6 @@
         <v>74.88</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
@@ -2896,7 +4031,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -2973,7 +4107,6 @@
       <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2994,7 +4127,6 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3015,7 +4147,6 @@
       <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3036,7 +4167,6 @@
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3057,7 +4187,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3078,7 +4207,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3099,7 +4227,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3135,7 +4262,6 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3159,7 +4285,6 @@
       <c r="H12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3245,7 +4370,6 @@
       <c r="G15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3300,7 +4424,6 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3386,7 +4509,6 @@
       <c r="H20" t="n">
         <v>0.99</v>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3425,7 +4547,6 @@
       <c r="J21" t="n">
         <v>0.95</v>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3514,7 +4635,6 @@
       <c r="H24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3547,7 +4667,6 @@
       <c r="H25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3568,7 +4687,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3598,7 +4716,6 @@
       <c r="H27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3662,7 +4779,6 @@
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3683,7 +4799,6 @@
       <c r="D30" t="n">
         <v>0.06</v>
       </c>
-      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3744,7 +4859,6 @@
       <c r="J32" t="n">
         <v>0.99</v>
       </c>
-      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3892,7 +5006,6 @@
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3994,7 +5107,6 @@
       <c r="G41" t="n">
         <v>0.01</v>
       </c>
-      <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4015,7 +5127,6 @@
       <c r="H42" t="n">
         <v>0.17</v>
       </c>
-      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4036,7 +5147,6 @@
       <c r="G43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4063,7 +5173,6 @@
       <c r="J44" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4148,7 +5257,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5287,7 +6395,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5452,7 +6559,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
@@ -5631,7 +6737,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>

--- a/claude/data/한양이엔지_데이터북_2026-10-22.xlsx
+++ b/claude/data/한양이엔지_데이터북_2026-10-22.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_밸류에이션" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_출처" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_현장일정표_정리" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_매출추정_28E" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_주가드라이버" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +46,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +68,11 @@
         <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F8BE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -75,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -85,6 +96,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1972,6 +1987,911 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>단일 강세 시나리오. 2023~25A는 DART 연결/별도, 2026~28E는 추정(가정). 단위 억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2023A</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>2024A</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>2025A</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>국내(별도) 매출</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>9089</v>
+      </c>
+      <c r="C4" t="n">
+        <v>9854</v>
+      </c>
+      <c r="D4" t="n">
+        <v>8764</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>9400</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  진행 현장(P4·M15X 등)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>4700</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P5</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  용인 Y1</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>300</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  기타 신규(삼성 용인1호 등)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  상시 Hook-up·유지보수·전환투자</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>3100</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  해외 CDS 수출</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>600</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  기타(플랜트·우주·디스플레이)</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  별도 OPM(%)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  별도 영업이익</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>778</v>
+      </c>
+      <c r="C13" t="n">
+        <v>724</v>
+      </c>
+      <c r="D13" t="n">
+        <v>329</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>423</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>875</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>해외(자회사) 매출</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1173</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2008</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2418</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4600</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  미국 테일러1</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  미국 테일러2·오스틴</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  HCM(CCSS 운영)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  중국·베트남·기타</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>650</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자회사 OPM(%)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  자회사 영업이익</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>73</v>
+      </c>
+      <c r="C20" t="n">
+        <v>138</v>
+      </c>
+      <c r="D20" t="n">
+        <v>208</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>552</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>605</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>연결 매출</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>10262</v>
+      </c>
+      <c r="C21" t="n">
+        <v>11862</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11182</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>21500</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  YoY(%)</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-5.7</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>연결 영업이익</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>851</v>
+      </c>
+      <c r="C23" t="n">
+        <v>862</v>
+      </c>
+      <c r="D23" t="n">
+        <v>537</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>975</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>1480</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  OPM(%)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>지배순이익</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>774</v>
+      </c>
+      <c r="C25" t="n">
+        <v>763</v>
+      </c>
+      <c r="D25" t="n">
+        <v>418</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>854</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>1248</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>EPS(원, 17.5M주)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4423</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4360</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2389</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>4880</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>7131</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>8783</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>교차검증: 2사 CAPEX(조)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="C27" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>80.17</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>119.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  매출/CAPEX(%)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>상관계수(분기 평균, 로그 레벨, 2016~2026)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr"/>
+      <c r="C1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>수주잔고(2018.12~)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>27분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>영업이익 최근4Q</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>영업이익 향후4Q</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>분기 변화율 상관</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>영업이익 최근4Q</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>수주잔고</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>공시 반응(D0~D+2, KOSDAQ 대비 초과수익 %)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P3 PH3 일반배관 1,120억(2022.06)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>테일러 CCSS 1,295억(2023.07)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>새 시장</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P4 PH1 일반배관 1,415억(2024.02)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>해외 CDS 1,214억(2026.05)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>고객 비공개</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>P5 Ph1 일반배관 1,481억(2026.09)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3Q25 분기보고서</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025 실적 30%변동 공시(2026.02)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>최대주주변경(신탁)+우주 사절단(2026.01.27)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>테마</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>FIL 5%(2026.09)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>누리호 4차 발사(2025.11)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
